--- a/grupos/6AEM - Estadisticos 20232.xlsx
+++ b/grupos/6AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
+    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>León González Ruth</t>
   </si>
   <si>
@@ -209,73 +209,58 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NERI</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
   </si>
   <si>
     <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
+    <t>AYLIN MELISSA</t>
   </si>
 </sst>
 </file>
@@ -783,22 +768,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -819,10 +804,10 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -860,22 +845,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -908,10 +893,10 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -937,22 +922,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -988,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1014,22 +999,22 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1050,19 +1035,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1091,22 +1076,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1133,16 +1118,16 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1168,22 +1153,22 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1204,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1219,7 +1204,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1245,22 +1230,22 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1281,10 +1266,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1293,7 +1278,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1322,22 +1307,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1361,7 +1346,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1399,22 +1384,22 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1435,19 +1420,19 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>5</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1476,22 +1461,22 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1512,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1524,10 +1509,10 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1553,22 +1538,22 @@
         <v>4</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1592,16 +1577,16 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1630,22 +1615,22 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1666,16 +1651,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1707,22 +1692,22 @@
         <v>4</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1749,10 +1734,10 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1784,22 +1769,22 @@
         <v>4</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1820,16 +1805,16 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>5</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -1861,22 +1846,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1897,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -1909,10 +1894,10 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1938,22 +1923,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1974,13 +1959,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>10</v>
@@ -2015,22 +2000,22 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2092,22 +2077,22 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2128,10 +2113,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2140,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2169,22 +2154,22 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2246,22 +2231,22 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2282,10 +2267,10 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2294,10 +2279,10 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2323,22 +2308,22 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2359,19 +2344,19 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2400,22 +2385,22 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2436,10 +2421,10 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2477,22 +2462,22 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2516,7 +2501,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2554,22 +2539,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2590,7 +2575,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2602,7 +2587,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2631,22 +2616,22 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2667,7 +2652,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2679,7 +2664,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2708,22 +2693,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2744,7 +2729,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -2756,7 +2741,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2785,22 +2770,22 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2821,16 +2806,16 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -2862,22 +2847,22 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2898,7 +2883,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -2910,7 +2895,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -2939,22 +2924,22 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2975,22 +2960,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>7</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3016,22 +3001,22 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3067,7 +3052,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3203,7 +3188,7 @@
         <v>80</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3212,16 +3197,16 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L4">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3230,13 +3215,13 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R4">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S4">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3262,7 +3247,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -3271,16 +3256,16 @@
         <v>85.7</v>
       </c>
       <c r="K5">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="L5">
-        <v>93.3</v>
+        <v>87.3</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3289,10 +3274,10 @@
         <v>85.7</v>
       </c>
       <c r="Q5">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="R5">
-        <v>93.3</v>
+        <v>87.3</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3321,16 +3306,16 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="I6">
         <v>100</v>
       </c>
       <c r="J6">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3339,16 +3324,16 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q6">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3380,37 +3365,37 @@
         <v>88</v>
       </c>
       <c r="H7">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="I7">
         <v>100</v>
       </c>
       <c r="J7">
-        <v>66.7</v>
+        <v>76.2</v>
       </c>
       <c r="K7">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="L7">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M7">
         <v>88</v>
       </c>
       <c r="N7">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>66.7</v>
+        <v>76.2</v>
       </c>
       <c r="Q7">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="R7">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S7">
         <v>88</v>
@@ -3439,37 +3424,37 @@
         <v>92</v>
       </c>
       <c r="H8">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="L8">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="M8">
         <v>92</v>
       </c>
       <c r="N8">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R8">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="S8">
         <v>92</v>
@@ -3498,7 +3483,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -3516,7 +3501,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3557,7 +3542,7 @@
         <v>80</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I10">
         <v>100</v>
@@ -3572,10 +3557,10 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3590,7 +3575,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3616,37 +3601,37 @@
         <v>80</v>
       </c>
       <c r="H11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I11">
         <v>100</v>
       </c>
       <c r="J11">
-        <v>76.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K11">
         <v>87.5</v>
       </c>
       <c r="L11">
-        <v>86.7</v>
+        <v>78.2</v>
       </c>
       <c r="M11">
         <v>80</v>
       </c>
       <c r="N11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>76.2</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q11">
         <v>87.5</v>
       </c>
       <c r="R11">
-        <v>86.7</v>
+        <v>78.2</v>
       </c>
       <c r="S11">
         <v>80</v>
@@ -3675,40 +3660,40 @@
         <v>80</v>
       </c>
       <c r="H12">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="I12">
         <v>100</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="L12">
-        <v>90</v>
+        <v>78.2</v>
       </c>
       <c r="M12">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N12">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R12">
-        <v>90</v>
+        <v>78.2</v>
       </c>
       <c r="S12">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3793,40 +3778,40 @@
         <v>60</v>
       </c>
       <c r="H14">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="I14">
         <v>100</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L14">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="M14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N14">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R14">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="S14">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3852,16 +3837,16 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="I15">
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3870,16 +3855,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3911,7 +3896,7 @@
         <v>60</v>
       </c>
       <c r="H16">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3923,14 +3908,14 @@
         <v>100</v>
       </c>
       <c r="L16">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="M16">
+        <v>72</v>
+      </c>
+      <c r="N16">
         <v>83.3</v>
       </c>
-      <c r="M16">
-        <v>60</v>
-      </c>
-      <c r="N16">
-        <v>73.3</v>
-      </c>
       <c r="O16">
         <v>100</v>
       </c>
@@ -3941,10 +3926,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>83.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S16">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3970,40 +3955,40 @@
         <v>60</v>
       </c>
       <c r="H17">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>66.7</v>
+        <v>76.2</v>
       </c>
       <c r="K17">
         <v>87.5</v>
       </c>
       <c r="L17">
-        <v>73.3</v>
+        <v>65.5</v>
       </c>
       <c r="M17">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N17">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>66.7</v>
+        <v>76.2</v>
       </c>
       <c r="Q17">
         <v>87.5</v>
       </c>
       <c r="R17">
-        <v>73.3</v>
+        <v>65.5</v>
       </c>
       <c r="S17">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4029,7 +4014,7 @@
         <v>72</v>
       </c>
       <c r="H18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -4038,16 +4023,16 @@
         <v>85.7</v>
       </c>
       <c r="K18">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="L18">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="M18">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N18">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4056,13 +4041,13 @@
         <v>85.7</v>
       </c>
       <c r="Q18">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="R18">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="S18">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4094,16 +4079,16 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L19">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M19">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N19">
         <v>86.7</v>
@@ -4112,16 +4097,16 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R19">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S19">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4147,40 +4132,40 @@
         <v>60</v>
       </c>
       <c r="H20">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J20">
         <v>81</v>
       </c>
       <c r="K20">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="L20">
-        <v>83.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="M20">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N20">
-        <v>73.3</v>
+        <v>80</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="P20">
         <v>81</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>88.8</v>
       </c>
       <c r="R20">
-        <v>83.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S20">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4206,7 +4191,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -4224,7 +4209,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4265,40 +4250,40 @@
         <v>60</v>
       </c>
       <c r="H22">
-        <v>96.7</v>
+        <v>88.3</v>
       </c>
       <c r="I22">
         <v>100</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="M22">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="N22">
-        <v>96.7</v>
+        <v>88.3</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R22">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="S22">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4336,7 +4321,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -4354,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4383,40 +4368,40 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>83.3</v>
+        <v>88.3</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N24">
-        <v>83.3</v>
+        <v>88.3</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4442,40 +4427,40 @@
         <v>80</v>
       </c>
       <c r="H25">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="I25">
         <v>100</v>
       </c>
       <c r="J25">
-        <v>85.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N25">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>85.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R25">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="S25">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4501,7 +4486,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -4513,13 +4498,13 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4531,7 +4516,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4619,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -4637,7 +4622,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4678,7 +4663,7 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -4687,16 +4672,16 @@
         <v>85.7</v>
       </c>
       <c r="K29">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="L29">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="M29">
         <v>100</v>
       </c>
       <c r="N29">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -4705,10 +4690,10 @@
         <v>85.7</v>
       </c>
       <c r="Q29">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="R29">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -4737,40 +4722,40 @@
         <v>60</v>
       </c>
       <c r="H30">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="I30">
         <v>100</v>
       </c>
       <c r="J30">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="K30">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="M30">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="N30">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>85.7</v>
+        <v>83.3</v>
       </c>
       <c r="Q30">
-        <v>95</v>
+        <v>91.3</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="S30">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4802,7 +4787,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -4820,7 +4805,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -4861,7 +4846,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -4870,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -4879,7 +4864,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>95.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -4888,7 +4873,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5004,7 +4989,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -5036,7 +5021,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5057,7 +5042,7 @@
         <v>23.3</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5068,7 +5053,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5089,7 +5074,7 @@
         <v>16.7</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5100,7 +5085,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5109,16 +5094,16 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="G5" s="2">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="H5">
         <v>7</v>
@@ -5153,7 +5138,7 @@
         <v>3.3</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5235,7 +5220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5267,22 +5252,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920162</v>
+        <v>21330051920153</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5290,22 +5275,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920162</v>
+        <v>21330051920153</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5319,16 +5304,16 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5342,16 +5327,16 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5365,16 +5350,16 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5388,16 +5373,16 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5411,16 +5396,16 @@
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5428,22 +5413,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920153</v>
+        <v>21330051920162</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5451,70 +5436,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920159</v>
+        <v>20330051920069</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920166</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920175</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20232.xlsx
+++ b/grupos/6AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="72">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
+    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>León González Ruth</t>
   </si>
   <si>
@@ -209,58 +209,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>AGUILAR</t>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
   </si>
   <si>
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
   </si>
   <si>
     <t>YAHIR</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
   </si>
 </sst>
 </file>
@@ -786,22 +759,22 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -813,10 +786,10 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -863,40 +836,40 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -940,22 +913,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1017,22 +990,22 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1094,22 +1067,22 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1124,7 +1097,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1171,22 +1144,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1204,7 +1177,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1248,22 +1221,22 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1325,22 +1298,22 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1349,7 +1322,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1402,28 +1375,28 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1432,7 +1405,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1479,22 +1452,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1556,22 +1529,22 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1589,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1633,22 +1606,22 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1666,7 +1639,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1710,25 +1683,25 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1743,7 +1716,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1787,31 +1760,31 @@
         <v>4</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1864,22 +1837,22 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -1891,7 +1864,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -1941,34 +1914,34 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>6</v>
@@ -2018,40 +1991,40 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>5</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2095,22 +2068,22 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2172,22 +2145,22 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -2196,13 +2169,13 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2249,22 +2222,22 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2282,7 +2255,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2326,37 +2299,37 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2403,22 +2376,22 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>8</v>
@@ -2433,10 +2406,10 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2480,28 +2453,28 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>9</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2510,10 +2483,10 @@
         <v>10</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2557,22 +2530,22 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2634,22 +2607,22 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2664,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2711,28 +2684,28 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2744,7 +2717,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2788,28 +2761,28 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>9</v>
@@ -2818,10 +2791,10 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2865,22 +2838,22 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -2942,28 +2915,28 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>8</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3019,22 +2992,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3052,7 +3025,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3206,7 +3179,7 @@
         <v>86</v>
       </c>
       <c r="N4">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3215,13 +3188,13 @@
         <v>100</v>
       </c>
       <c r="Q4">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R4">
         <v>95</v>
       </c>
-      <c r="R4">
-        <v>96.40000000000001</v>
-      </c>
       <c r="S4">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3265,19 +3238,19 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>85.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>91.3</v>
+        <v>94.5</v>
       </c>
       <c r="R5">
-        <v>87.3</v>
+        <v>88.8</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -3324,16 +3297,16 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3383,22 +3356,22 @@
         <v>88</v>
       </c>
       <c r="N7">
-        <v>81.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
       </c>
       <c r="P7">
-        <v>76.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="R7">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="S7">
-        <v>88</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3442,22 +3415,22 @@
         <v>92</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>90.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R8">
-        <v>85.5</v>
+        <v>88.8</v>
       </c>
       <c r="S8">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3501,7 +3474,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3560,7 +3533,7 @@
         <v>86</v>
       </c>
       <c r="N10">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3575,7 +3548,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3619,22 +3592,22 @@
         <v>80</v>
       </c>
       <c r="N11">
-        <v>85</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>78.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q11">
+        <v>92.2</v>
+      </c>
+      <c r="R11">
+        <v>82.5</v>
+      </c>
+      <c r="S11">
         <v>87.5</v>
-      </c>
-      <c r="R11">
-        <v>78.2</v>
-      </c>
-      <c r="S11">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3678,22 +3651,22 @@
         <v>86</v>
       </c>
       <c r="N12">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O12">
         <v>100</v>
       </c>
       <c r="P12">
-        <v>90.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q12">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R12">
-        <v>78.2</v>
+        <v>83.8</v>
       </c>
       <c r="S12">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3796,22 +3769,22 @@
         <v>80</v>
       </c>
       <c r="N14">
-        <v>81.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O14">
         <v>100</v>
       </c>
       <c r="P14">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="Q14">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="R14">
         <v>95</v>
       </c>
-      <c r="R14">
-        <v>92.7</v>
-      </c>
       <c r="S14">
-        <v>80</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3855,16 +3828,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="Q15">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3914,7 +3887,7 @@
         <v>72</v>
       </c>
       <c r="N16">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3926,10 +3899,10 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>70.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="S16">
-        <v>72</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3973,22 +3946,22 @@
         <v>72</v>
       </c>
       <c r="N17">
-        <v>81.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>76.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q17">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="R17">
-        <v>65.5</v>
+        <v>76.3</v>
       </c>
       <c r="S17">
-        <v>72</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4032,22 +4005,22 @@
         <v>86</v>
       </c>
       <c r="N18">
-        <v>85</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>85.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q18">
+        <v>94.5</v>
+      </c>
+      <c r="R18">
+        <v>86.3</v>
+      </c>
+      <c r="S18">
         <v>91.3</v>
-      </c>
-      <c r="R18">
-        <v>81.8</v>
-      </c>
-      <c r="S18">
-        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4091,22 +4064,22 @@
         <v>86</v>
       </c>
       <c r="N19">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <v>90.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
-        <v>70.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="S19">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4150,22 +4123,22 @@
         <v>72</v>
       </c>
       <c r="N20">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="O20">
+        <v>81.3</v>
+      </c>
+      <c r="P20">
+        <v>87.5</v>
+      </c>
+      <c r="Q20">
+        <v>93</v>
+      </c>
+      <c r="R20">
         <v>80</v>
       </c>
-      <c r="O20">
-        <v>70</v>
-      </c>
-      <c r="P20">
-        <v>81</v>
-      </c>
-      <c r="Q20">
-        <v>88.8</v>
-      </c>
-      <c r="R20">
-        <v>70.90000000000001</v>
-      </c>
       <c r="S20">
-        <v>72</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4209,7 +4182,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4268,22 +4241,22 @@
         <v>70</v>
       </c>
       <c r="N22">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="Q22">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R22">
-        <v>94.5</v>
+        <v>95</v>
       </c>
       <c r="S22">
-        <v>70</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4339,7 +4312,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4386,22 +4359,22 @@
         <v>96</v>
       </c>
       <c r="N24">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S24">
-        <v>96</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4445,22 +4418,22 @@
         <v>86</v>
       </c>
       <c r="N25">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>88.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="Q25">
+        <v>97.7</v>
+      </c>
+      <c r="R25">
         <v>96.3</v>
       </c>
-      <c r="R25">
-        <v>94.5</v>
-      </c>
       <c r="S25">
-        <v>86</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4504,7 +4477,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4516,7 +4489,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4622,7 +4595,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -4681,19 +4654,19 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>85</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>85.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q29">
-        <v>93.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R29">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -4740,22 +4713,22 @@
         <v>76</v>
       </c>
       <c r="N30">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>83.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q30">
-        <v>91.3</v>
+        <v>94.5</v>
       </c>
       <c r="R30">
-        <v>85.5</v>
+        <v>90</v>
       </c>
       <c r="S30">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4805,7 +4778,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -4864,7 +4837,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -4873,7 +4846,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>94</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4989,7 +4962,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -4998,19 +4971,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5021,7 +4994,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5030,19 +5003,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>76.7</v>
+        <v>90</v>
       </c>
       <c r="G3" s="2">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5053,7 +5026,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5062,19 +5035,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>83.3</v>
+        <v>93.3</v>
       </c>
       <c r="G4" s="2">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5085,7 +5058,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5094,19 +5067,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5126,19 +5099,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5158,19 +5131,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5220,7 +5193,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5252,19 +5225,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920153</v>
+        <v>21330051920164</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
@@ -5275,22 +5248,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920153</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
         <v>69</v>
       </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5298,22 +5271,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920171</v>
+        <v>21330051920165</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" t="s">
-        <v>76</v>
-      </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5321,22 +5294,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920171</v>
+        <v>21330051920165</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
       </c>
       <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5344,116 +5317,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920176</v>
+        <v>21330051920171</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
         <v>71</v>
       </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>54</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920176</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920001</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920069</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
